--- a/data.xlsx
+++ b/data.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F109"/>
+  <dimension ref="A1:F216"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3902,6 +3902,3430 @@
         </is>
       </c>
       <c r="F109" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>Ned Lamont</t>
+        </is>
+      </c>
+      <c r="B110" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C110" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E110" t="inlineStr">
+        <is>
+          <t>Incumbent</t>
+        </is>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>Ashley Hinson</t>
+        </is>
+      </c>
+      <c r="B111" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C111" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E111" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>Jim Carlin</t>
+        </is>
+      </c>
+      <c r="B112" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C112" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E112" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>Joshua Smith</t>
+        </is>
+      </c>
+      <c r="B113" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C113" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E113" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>John Berman</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C114" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>Zach Wahls</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C115" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>Dem Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>Josh Turek</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C116" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>Chris Henry</t>
+        </is>
+      </c>
+      <c r="B117" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C117" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E117" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>Bob Krause</t>
+        </is>
+      </c>
+      <c r="B118" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C118" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E118" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>JB Pritzker</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C119" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Incumbent</t>
+        </is>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>Patricia Tillman</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C120" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>Removed from ballot (insufficient signatures)</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>Darren Bailey</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C121" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>Ted Dabrowski</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C122" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E122" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>Rick Heidner</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C123" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>James Mendrick</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>Illinois</t>
+        </is>
+      </c>
+      <c r="C124" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>Tina Kotek</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C125" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E125" t="inlineStr">
+        <is>
+          <t>Incumbent</t>
+        </is>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>Forest Alexander</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C126" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E126" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>James Atkinson</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C127" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E127" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>Brittany Jones</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C128" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D128" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>Tristan Sheppard</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C129" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D129" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>Christine Drazan</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C130" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D130" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>Chris Dudley</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C131" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D131" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E131" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>Danielle Bethell</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C132" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D132" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E132" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>Ed Diehl</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C133" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D133" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E133" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>David Medina</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C134" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E134" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>Hope Dalrymple</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C135" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E135" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>Kyle Duyck</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C136" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D136" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>Ned Lamont</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C137" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D137" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>Incumbent</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>Joshua Elliott</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C138" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>Ryan Fazio</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C139" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D139" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>naughty</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>Erin Stewart</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D140" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>GOP Primary Co-Frontrunner</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>Betsy McCaughey</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C141" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E141" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>Timothy Wilcox</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C142" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E142" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>Kelly Ayotte</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C143" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E143" t="inlineStr">
+        <is>
+          <t>Incumbent</t>
+        </is>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>Corey Lewandowski</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C144" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E144" t="inlineStr">
+        <is>
+          <t>GOP Potential Candidate</t>
+        </is>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>Cinde Warmington</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C145" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D145" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E145" t="inlineStr">
+        <is>
+          <t>Dem Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>Jonathan Kiper</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C146" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E146" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>Tom Sherman</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C147" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D147" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E147" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>Deaglan McEachern</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C148" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D148" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E148" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>Donovan Fenton</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C149" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D149" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E149" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>Jeff Colyer</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C150" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D150" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E150" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>Ty Masterson</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C151" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D151" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E151" t="inlineStr">
+        <is>
+          <t>GOP Primary Co-Frontrunner</t>
+        </is>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Scott Schwab</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C152" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D152" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Vicki Schmidt</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C153" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D153" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Charlotte O'Hara</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C154" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D154" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Stacy Rogers</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C155" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D155" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Philip Sarnecki</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C156" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D156" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Cindy Holscher</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C157" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>Dem Primary Co-Frontrunner</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Ethan Corson</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C158" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D158" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>Dem Primary Co-Frontrunner</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Marty Tuley</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C159" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D159" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E159" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Deb Haaland</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C160" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D160" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E160" t="inlineStr">
+        <is>
+          <t>Dem Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Sam Bregman</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C161" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D161" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E161" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Ken Miyagishima</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C162" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D162" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E162" t="inlineStr">
+        <is>
+          <t>Independent Candidate</t>
+        </is>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Gregg Hull</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C163" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D163" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E163" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Duke Rodriguez</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C164" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E164" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Steve Lanier</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C165" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D165" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E165" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Doug Turner</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C166" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E166" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Randy Feenstra</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C167" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E167" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Eddie Andrews</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C168" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E168" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Zach Lahn</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C169" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E169" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Brad Sherman</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C170" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E170" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Adam Steen</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C171" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E171" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Rob Sand</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C172" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E172" t="inlineStr">
+        <is>
+          <t>Dem Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Julie Stauch</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C173" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E173" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Paul Dahl</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C174" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E174" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Nirav Shah</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>Dem Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Angus King III</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D176" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>Dem Primary Co-Frontrunner</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Hannah Pingree</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Shenna Bellows</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D178" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Troy Jackson</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D179" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Eloise Vitelli</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D180" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>Dem Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Bobby Charles</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>Garrett Mason</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D182" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>James Libby</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D183" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Owen McCarthy</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Jonathan Bush</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D185" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Ben Midgley</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>David Jones</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D187" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Robert Wessels</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Kenneth Capron</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D189" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Derek Levasseur</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D190" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Alexander Murchison</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D191" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Richard Bennett</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D192" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>Independent Candidate</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>W. Edward Crockett</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C193" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D193" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E193" t="inlineStr">
+        <is>
+          <t>Independent Candidate</t>
+        </is>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>John Glowa</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C194" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D194" t="inlineStr">
+        <is>
+          <t>I</t>
+        </is>
+      </c>
+      <c r="E194" t="inlineStr">
+        <is>
+          <t>Independent Candidate</t>
+        </is>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>Cory Booker</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C195" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D195" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E195" t="inlineStr">
+        <is>
+          <t>Incumbent</t>
+        </is>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>Alex Zdan</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C196" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D196" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E196" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>Justin Murphy</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C197" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D197" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E197" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>Richard Tabor</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C198" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D198" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E198" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>Natalie Rivera</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C199" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D199" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E199" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>Robert Lebovics</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C200" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D200" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E200" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>Andy Barr</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C201" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E201" t="inlineStr">
+        <is>
+          <t>Open Seat Candidate</t>
+        </is>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>Daniel Cameron</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C202" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E202" t="inlineStr">
+        <is>
+          <t>Open Seat Candidate</t>
+        </is>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>Nate Morris</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C203" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E203" t="inlineStr">
+        <is>
+          <t>Open Seat Candidate</t>
+        </is>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>nice</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>Charles Booker</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C204" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D204" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E204" t="inlineStr">
+        <is>
+          <t>Open Seat Candidate</t>
+        </is>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>Amy McGrath</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C205" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D205" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E205" t="inlineStr">
+        <is>
+          <t>Open Seat Candidate</t>
+        </is>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>Pamela Stevenson</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C206" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D206" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E206" t="inlineStr">
+        <is>
+          <t>Open Seat Candidate</t>
+        </is>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>Cory Booker</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C207" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D207" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E207" t="inlineStr">
+        <is>
+          <t>Incumbent</t>
+        </is>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>Alex Zdan</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C208" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D208" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E208" t="inlineStr">
+        <is>
+          <t>GOP Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>Justin Murphy</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C209" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D209" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E209" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>Richard Tabor</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C210" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D210" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E210" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>Natalie Rivera</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C211" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D211" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E211" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="212">
+      <c r="A212" t="inlineStr">
+        <is>
+          <t>Robert Lebovics</t>
+        </is>
+      </c>
+      <c r="B212" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C212" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D212" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E212" t="inlineStr">
+        <is>
+          <t>GOP Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F212" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="213">
+      <c r="A213" t="inlineStr">
+        <is>
+          <t>Ashley Moody</t>
+        </is>
+      </c>
+      <c r="B213" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C213" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D213" t="inlineStr">
+        <is>
+          <t>R</t>
+        </is>
+      </c>
+      <c r="E213" t="inlineStr">
+        <is>
+          <t>Appointed Incumbent</t>
+        </is>
+      </c>
+      <c r="F213" t="inlineStr">
+        <is>
+          <t>nuanced</t>
+        </is>
+      </c>
+    </row>
+    <row r="214">
+      <c r="A214" t="inlineStr">
+        <is>
+          <t>Alex Vindman</t>
+        </is>
+      </c>
+      <c r="B214" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C214" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D214" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E214" t="inlineStr">
+        <is>
+          <t>Democratic Primary Frontrunner</t>
+        </is>
+      </c>
+      <c r="F214" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="215">
+      <c r="A215" t="inlineStr">
+        <is>
+          <t>Angie Nixon</t>
+        </is>
+      </c>
+      <c r="B215" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C215" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D215" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E215" t="inlineStr">
+        <is>
+          <t>Democratic Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F215" t="inlineStr">
+        <is>
+          <t>no_record</t>
+        </is>
+      </c>
+    </row>
+    <row r="216">
+      <c r="A216" t="inlineStr">
+        <is>
+          <t>Alan Grayson</t>
+        </is>
+      </c>
+      <c r="B216" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C216" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D216" t="inlineStr">
+        <is>
+          <t>D</t>
+        </is>
+      </c>
+      <c r="E216" t="inlineStr">
+        <is>
+          <t>Democratic Primary Candidate</t>
+        </is>
+      </c>
+      <c r="F216" t="inlineStr">
         <is>
           <t>no_record</t>
         </is>
@@ -3918,7 +7342,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C282"/>
+  <dimension ref="A1:C413"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8712,6 +12136,2233 @@
       <c r="C282" t="inlineStr">
         <is>
           <t>https://w4nevada.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="283">
+      <c r="A283" t="inlineStr">
+        <is>
+          <t>Ned Lamont</t>
+        </is>
+      </c>
+      <c r="B283" t="inlineStr">
+        <is>
+          <t>Twice blocked comprehensive AI accountability bills (2024, 2025) via veto threat after CT Senate passed them — citing innovation concerns and business competitiveness; House declined to bring bills to floor vote as a result</t>
+        </is>
+      </c>
+      <c r="C283" t="inlineStr">
+        <is>
+          <t>https://fortune.com/2024/05/09/connecticut-ai-law-veto-threat-lamont-us-ai-regulation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="284">
+      <c r="A284" t="inlineStr">
+        <is>
+          <t>Ned Lamont</t>
+        </is>
+      </c>
+      <c r="B284" t="inlineStr">
+        <is>
+          <t>Signed narrower AI protections: government AI disclosure law (2023), data privacy amendment requiring disclosure of AI/LLM training use (2025), deepfake revenge porn criminalization (2025), and $500K AI workforce education funding</t>
+        </is>
+      </c>
+      <c r="C284" t="inlineStr">
+        <is>
+          <t>https://ctmirror.org/2025/07/14/ct-ai-laws-session/</t>
+        </is>
+      </c>
+    </row>
+    <row r="285">
+      <c r="A285" t="inlineStr">
+        <is>
+          <t>Ned Lamont</t>
+        </is>
+      </c>
+      <c r="B285" t="inlineStr">
+        <is>
+          <t>Proposed SB 86 (2026): requires AI chatbots to detect mental health distress and refer users to crisis services, remind users every 2hrs they are talking to AI; also creates AI regulatory sandbox to promote adoption in insurance/finance/health</t>
+        </is>
+      </c>
+      <c r="C285" t="inlineStr">
+        <is>
+          <t>https://hartfordbusiness.com/article/lamont-proposes-bill-to-protect-kids-from-ai-chatbots-create-ai-development-sandbox/</t>
+        </is>
+      </c>
+    </row>
+    <row r="286">
+      <c r="A286" t="inlineStr">
+        <is>
+          <t>Ned Lamont</t>
+        </is>
+      </c>
+      <c r="B286" t="inlineStr">
+        <is>
+          <t>Stated he does not want to "slow up innovation and make that smart, young programmer think that maybe it's a little safer to do this in Georgia" — frames comprehensive AI regulation as economic risk; argues regulation should be federal not state-level</t>
+        </is>
+      </c>
+      <c r="C286" t="inlineStr">
+        <is>
+          <t>https://ctmirror.org/2026/01/28/artificial-intelligence-regulation-senate-lamont-ct/</t>
+        </is>
+      </c>
+    </row>
+    <row r="287">
+      <c r="A287" t="inlineStr">
+        <is>
+          <t>Ashley Hinson</t>
+        </is>
+      </c>
+      <c r="B287" t="inlineStr">
+        <is>
+          <t>Co-led bipartisan bill to strip Section 230 protections from platforms failing to remove AI deepfake pornography; stated deepfakes present "significant and growing threat" and "Big Tech companies shouldn't be able to hide behind Section 230"</t>
+        </is>
+      </c>
+      <c r="C287" t="inlineStr">
+        <is>
+          <t>https://www.thegazette.com/government-politics/iowas-ashley-hinson-introduces-bill-to-combat-ai-deepfakes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="288">
+      <c r="A288" t="inlineStr">
+        <is>
+          <t>Ashley Hinson</t>
+        </is>
+      </c>
+      <c r="B288" t="inlineStr">
+        <is>
+          <t>Joined Child Exploitation and Artificial Intelligence Expert Commission Act to create legal framework for law enforcement to combat AI-generated CSAM; stated "we need to be proactive — not reactive — about this potential danger"</t>
+        </is>
+      </c>
+      <c r="C288" t="inlineStr">
+        <is>
+          <t>https://hinson.house.gov/media/press-releases/hinson-joins-bipartisan-effort-protect-children-exploitation-through-ai</t>
+        </is>
+      </c>
+    </row>
+    <row r="289">
+      <c r="A289" t="inlineStr">
+        <is>
+          <t>Ashley Hinson</t>
+        </is>
+      </c>
+      <c r="B289" t="inlineStr">
+        <is>
+          <t>As House Select Committee on China member, called it "critical for national security that the U.S. beat the Chinese Communist Party on AI"; advocated strengthening export controls on advanced AI chips to China — frames AI primarily as competitiveness issue</t>
+        </is>
+      </c>
+      <c r="C289" t="inlineStr">
+        <is>
+          <t>https://punchbowl.news/the-ones-to-watch/advancing-with-ai/ashley-hinson/</t>
+        </is>
+      </c>
+    </row>
+    <row r="290">
+      <c r="A290" t="inlineStr">
+        <is>
+          <t>Ashley Hinson</t>
+        </is>
+      </c>
+      <c r="B290" t="inlineStr">
+        <is>
+          <t>Unveiled Workforce Innovation &amp; Empowerment package focused on upskilling workers for AI economy, especially non-college workers; no broader AI safety or algorithmic accountability legislation sponsored</t>
+        </is>
+      </c>
+      <c r="C290" t="inlineStr">
+        <is>
+          <t>https://punchbowl.news/the-ones-to-watch/advancing-with-ai/ashley-hinson/</t>
+        </is>
+      </c>
+    </row>
+    <row r="291">
+      <c r="A291" t="inlineStr">
+        <is>
+          <t>Zach Wahls</t>
+        </is>
+      </c>
+      <c r="B291" t="inlineStr">
+        <is>
+          <t>Campaign platform mentions only "proper regulation of technology and how our personal data is used" — no mention of AI, deepfakes, algorithmic accountability, or automation anywhere on issues page; top priorities are healthcare, education, workers rights</t>
+        </is>
+      </c>
+      <c r="C291" t="inlineStr">
+        <is>
+          <t>https://zachwahls.com/issues/</t>
+        </is>
+      </c>
+    </row>
+    <row r="292">
+      <c r="A292" t="inlineStr">
+        <is>
+          <t>Zach Wahls</t>
+        </is>
+      </c>
+      <c r="B292" t="inlineStr">
+        <is>
+          <t>Serves on Iowa Senate Technology Committee (minority member); supported Iowa Consumer Data Protection Act (SF 262, 2023) but did not sponsor it; no AI-specific bills sponsored or co-sponsored found in Iowa legislative record</t>
+        </is>
+      </c>
+      <c r="C292" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Zach_Wahls</t>
+        </is>
+      </c>
+    </row>
+    <row r="293">
+      <c r="A293" t="inlineStr">
+        <is>
+          <t>Jim Carlin</t>
+        </is>
+      </c>
+      <c r="B293" t="inlineStr">
+        <is>
+          <t>No AI-specific positions found; campaign focuses on antitrust, deregulation, and Trump legacy; supported social media censorship bill in state senate (content moderation, not AI)</t>
+        </is>
+      </c>
+      <c r="C293" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Jim_Carlin</t>
+        </is>
+      </c>
+    </row>
+    <row r="294">
+      <c r="A294" t="inlineStr">
+        <is>
+          <t>Joshua Smith</t>
+        </is>
+      </c>
+      <c r="B294" t="inlineStr">
+        <is>
+          <t>No AI positions found; platform is Ron Paul-style libertarianism (end federal gun laws, end foreign aid, economic freedom); minimal campaign infrastructure, no FEC filings as of March 2026</t>
+        </is>
+      </c>
+      <c r="C294" t="inlineStr">
+        <is>
+          <t>https://joshuasmith4senate.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="295">
+      <c r="A295" t="inlineStr">
+        <is>
+          <t>John Berman</t>
+        </is>
+      </c>
+      <c r="B295" t="inlineStr">
+        <is>
+          <t>No AI positions or policy record found; perennial candidate with engineer background; no FEC filings and no completed candidate surveys as of March 2026</t>
+        </is>
+      </c>
+      <c r="C295" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/John_Berman</t>
+        </is>
+      </c>
+    </row>
+    <row r="296">
+      <c r="A296" t="inlineStr">
+        <is>
+          <t>Josh Turek</t>
+        </is>
+      </c>
+      <c r="B296" t="inlineStr">
+        <is>
+          <t>No AI positions found; sitting Iowa House member and two-time Paralympic gold medalist; campaign centers on lowering costs, Medicaid, minimum wage, clean air/water; no AI bills sponsored in Iowa legislature</t>
+        </is>
+      </c>
+      <c r="C296" t="inlineStr">
+        <is>
+          <t>https://iowacapitaldispatch.com/2025/08/12/iowa-rep-josh-turek-two-time-paralympian-launches-campaign-for-u-s-senate/</t>
+        </is>
+      </c>
+    </row>
+    <row r="297">
+      <c r="A297" t="inlineStr">
+        <is>
+          <t>Chris Henry</t>
+        </is>
+      </c>
+      <c r="B297" t="inlineStr">
+        <is>
+          <t>No AI positions or public record found; low-profile candidate with minimal campaign infrastructure; no website or candidate survey responses found</t>
+        </is>
+      </c>
+      <c r="C297" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Chris_Henry_(Iowa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="298">
+      <c r="A298" t="inlineStr">
+        <is>
+          <t>Bob Krause</t>
+        </is>
+      </c>
+      <c r="B298" t="inlineStr">
+        <is>
+          <t>No AI positions found; perennial candidate and Army veteran, Iowa legislature 1973-1979; 2026 campaign focused exclusively on defending democracy, Constitution, and veterans issues</t>
+        </is>
+      </c>
+      <c r="C298" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Bob_Krause_(Iowa)</t>
+        </is>
+      </c>
+    </row>
+    <row r="299">
+      <c r="A299" t="inlineStr">
+        <is>
+          <t>JB Pritzker</t>
+        </is>
+      </c>
+      <c r="B299" t="inlineStr">
+        <is>
+          <t>Signed HB 3773 (Jan 2026): amended Illinois Human Rights Act to prohibit AI employment discrimination; employers must notify workers when AI is used in hiring/promotion/termination decisions</t>
+        </is>
+      </c>
+      <c r="C299" t="inlineStr">
+        <is>
+          <t>https://regulations.ai/regulations/illinois-hb-3773-ai-employment-discrimination-2024</t>
+        </is>
+      </c>
+    </row>
+    <row r="300">
+      <c r="A300" t="inlineStr">
+        <is>
+          <t>JB Pritzker</t>
+        </is>
+      </c>
+      <c r="B300" t="inlineStr">
+        <is>
+          <t>Signed HB 4875 and HB 4762 (Aug 2024): prohibited unauthorized AI-generated digital replicas of artists; made Illinois second state after Tennessee to protect creators from deepfakes</t>
+        </is>
+      </c>
+      <c r="C300" t="inlineStr">
+        <is>
+          <t>https://housewub.org/new-illinois-law-protects-artists-from-ai-generative-deepfakes/</t>
+        </is>
+      </c>
+    </row>
+    <row r="301">
+      <c r="A301" t="inlineStr">
+        <is>
+          <t>JB Pritzker</t>
+        </is>
+      </c>
+      <c r="B301" t="inlineStr">
+        <is>
+          <t>Signed HB 1806 (Aug 2025): nation's first law banning unlicensed AI therapy chatbots; prohibits AI from performing mental health decisions without licensed clinician oversight; passed unanimously in both chambers</t>
+        </is>
+      </c>
+      <c r="C301" t="inlineStr">
+        <is>
+          <t>https://idfpr.illinois.gov/news/2025/gov-pritzker-signs-state-leg-prohibiting-ai-therapy-in-il.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="302">
+      <c r="A302" t="inlineStr">
+        <is>
+          <t>JB Pritzker</t>
+        </is>
+      </c>
+      <c r="B302" t="inlineStr">
+        <is>
+          <t>Pushed back against Trump executive order limiting state AI regulation (Dec 2025), calling it "unlawful" and "blatant federal overreach"; stated Illinois "won't back down" from state-level AI protections</t>
+        </is>
+      </c>
+      <c r="C302" t="inlineStr">
+        <is>
+          <t>https://capitolnewsillinois.com/news/illinois-leaders-wont-back-down-following-trumps-order-limiting-ai-regulation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="303">
+      <c r="A303" t="inlineStr">
+        <is>
+          <t>Darren Bailey</t>
+        </is>
+      </c>
+      <c r="B303" t="inlineStr">
+        <is>
+          <t>Proposed using AI to replace municipal office workers and consolidate administrative functions across ~900 Illinois school districts as government cost-cutting measure; no worker protections or regulatory guardrails mentioned</t>
+        </is>
+      </c>
+      <c r="C303" t="inlineStr">
+        <is>
+          <t>https://capitolnewsillinois.com/news/bailey-proposes-illinois-doge-as-republican-governors-race-focuses-on-spending/</t>
+        </is>
+      </c>
+    </row>
+    <row r="304">
+      <c r="A304" t="inlineStr">
+        <is>
+          <t>Darren Bailey</t>
+        </is>
+      </c>
+      <c r="B304" t="inlineStr">
+        <is>
+          <t>Proposed "Illinois DOGE" (Dept of Government Efficiency) with running mate as DOGE Czar; AI framed purely as efficiency tool; no AI safety, deepfake, or accountability positions found in Blueprint for Illinois platform</t>
+        </is>
+      </c>
+      <c r="C304" t="inlineStr">
+        <is>
+          <t>https://abc7chicago.com/post/2026-elections-darren-bailey-proposes-illinois-doge-policy-agenda-republican-governors-race-focuses-spending/18374342/</t>
+        </is>
+      </c>
+    </row>
+    <row r="305">
+      <c r="A305" t="inlineStr">
+        <is>
+          <t>Ted Dabrowski</t>
+        </is>
+      </c>
+      <c r="B305" t="inlineStr">
+        <is>
+          <t>No AI positions found; former Wirepoints/Illinois Policy Institute president; campaign focuses on fiscal policy and government reform</t>
+        </is>
+      </c>
+      <c r="C305" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Ted_Dabrowski</t>
+        </is>
+      </c>
+    </row>
+    <row r="306">
+      <c r="A306" t="inlineStr">
+        <is>
+          <t>Rick Heidner</t>
+        </is>
+      </c>
+      <c r="B306" t="inlineStr">
+        <is>
+          <t>No AI positions found; video gambling mogul and real estate developer; no technology policy record found</t>
+        </is>
+      </c>
+      <c r="C306" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Rick_Heidner</t>
+        </is>
+      </c>
+    </row>
+    <row r="307">
+      <c r="A307" t="inlineStr">
+        <is>
+          <t>James Mendrick</t>
+        </is>
+      </c>
+      <c r="B307" t="inlineStr">
+        <is>
+          <t>No AI positions found; two-term DuPage County Sheriff; campaign focused on public safety and law enforcement</t>
+        </is>
+      </c>
+      <c r="C307" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/James_Mendrick</t>
+        </is>
+      </c>
+    </row>
+    <row r="308">
+      <c r="A308" t="inlineStr">
+        <is>
+          <t>Patricia Tillman</t>
+        </is>
+      </c>
+      <c r="B308" t="inlineStr">
+        <is>
+          <t>No AI positions found; minor Democratic challenger with minimal campaign presence</t>
+        </is>
+      </c>
+      <c r="C308" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Illinois_gubernatorial_and_lieutenant_gubernatorial_election,_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="309">
+      <c r="A309" t="inlineStr">
+        <is>
+          <t>Patricia Tillman</t>
+        </is>
+      </c>
+      <c r="B309" t="inlineStr">
+        <is>
+          <t>Removed from March 2026 primary ballot after submitting ~3,400 valid signatures vs 5,000 required; no AI or technology policy positions found; campaign site minimal with no policy content</t>
+        </is>
+      </c>
+      <c r="C309" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Patricia_Tillman</t>
+        </is>
+      </c>
+    </row>
+    <row r="310">
+      <c r="A310" t="inlineStr">
+        <is>
+          <t>Tina Kotek</t>
+        </is>
+      </c>
+      <c r="B310" t="inlineStr">
+        <is>
+          <t>Created Oregon AI Advisory Council by executive order (Nov 2023) to develop a plan "that values transparency, privacy and equity"; council delivered 74-recommendation Final Action Plan in Feb 2025</t>
+        </is>
+      </c>
+      <c r="C310" t="inlineStr">
+        <is>
+          <t>https://oregoncapitalchronicle.com/2023/11/29/kotek-forms-oregon-advisory-council-to-guide-the-states-use-of-artificial-intelligence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="311">
+      <c r="A311" t="inlineStr">
+        <is>
+          <t>Tina Kotek</t>
+        </is>
+      </c>
+      <c r="B311" t="inlineStr">
+        <is>
+          <t>Directed $10M in Oregon CHIPS Act funding for AI/semiconductor workforce development and signed MOU with NVIDIA to deploy AI Ambassador Program across Oregon colleges (April 2025)</t>
+        </is>
+      </c>
+      <c r="C311" t="inlineStr">
+        <is>
+          <t>https://apps.oregon.gov/oregon-newsroom/OR/GOV/Posts/Post/governor-kotek-announces-collaboration-and-investment-to-foster-ai-workforce-and-economic-development</t>
+        </is>
+      </c>
+    </row>
+    <row r="312">
+      <c r="A312" t="inlineStr">
+        <is>
+          <t>Tina Kotek</t>
+        </is>
+      </c>
+      <c r="B312" t="inlineStr">
+        <is>
+          <t>SB 1546 passed Oregon legislature (Mar 2026, 28-2 Senate vote) and sent to her desk: requires AI chatbots to disclose identity, give break reminders, block explicit content for minors, prohibit addictive algorithms, and refer mental health users to crisis hotlines — includes private right of action</t>
+        </is>
+      </c>
+      <c r="C312" t="inlineStr">
+        <is>
+          <t>https://www.transparencycoalition.ai/news/oregon-lawmakers-pass-major-chatbot-bill-in-significant-win-for-kids-and-ai-safety</t>
+        </is>
+      </c>
+    </row>
+    <row r="313">
+      <c r="A313" t="inlineStr">
+        <is>
+          <t>Tina Kotek</t>
+        </is>
+      </c>
+      <c r="B313" t="inlineStr">
+        <is>
+          <t>Oregon passed HB 2299 (criminalizing AI-generated intimate deepfakes) and SB 1571 (requiring AI disclosure in political campaign ads) during her tenure; state employees given free generative AI training (July 2025)</t>
+        </is>
+      </c>
+      <c r="C313" t="inlineStr">
+        <is>
+          <t>https://nbc16.com/news/local/oregon-senate-passes-bill-criminalizing-ai-generated-intimate-images-deepfake-artificial-intelligence-pornography-revenge-porn-senate-oregon-salem-portland-house-governor-tina-kotek-victim-violence</t>
+        </is>
+      </c>
+    </row>
+    <row r="314">
+      <c r="A314" t="inlineStr">
+        <is>
+          <t>Christine Drazan</t>
+        </is>
+      </c>
+      <c r="B314" t="inlineStr">
+        <is>
+          <t>No AI policy positions found; campaign focuses on lowering taxes, cutting regulations, public safety; no AI statements, votes, or PAC connections documented; appointed to Oregon Senate Oct 2025 leaving limited legislative record</t>
+        </is>
+      </c>
+      <c r="C314" t="inlineStr">
+        <is>
+          <t>https://www.christinefororegon.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="315">
+      <c r="A315" t="inlineStr">
+        <is>
+          <t>Chris Dudley</t>
+        </is>
+      </c>
+      <c r="B315" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign centers on education, public safety, breaking Oregon "economic doom loop"; no AI PAC funding despite Phil Knight $1M donation</t>
+        </is>
+      </c>
+      <c r="C315" t="inlineStr">
+        <is>
+          <t>https://oregoncapitalchronicle.com/2026/01/26/chris-dudley-says-he-will-run-for-oregon-governor-growing-gop-field/</t>
+        </is>
+      </c>
+    </row>
+    <row r="316">
+      <c r="A316" t="inlineStr">
+        <is>
+          <t>Danielle Bethell</t>
+        </is>
+      </c>
+      <c r="B316" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign priorities are accountability, public safety, drug policy, housing, fiscal discipline</t>
+        </is>
+      </c>
+      <c r="C316" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Danielle_Bethell</t>
+        </is>
+      </c>
+    </row>
+    <row r="317">
+      <c r="A317" t="inlineStr">
+        <is>
+          <t>Ed Diehl</t>
+        </is>
+      </c>
+      <c r="B317" t="inlineStr">
+        <is>
+          <t>No AI record found; engineering background (Stanford mech eng, Concept Systems co-founder) but no AI policy statements; was excused during SB1546 AI chatbot bill vote</t>
+        </is>
+      </c>
+      <c r="C317" t="inlineStr">
+        <is>
+          <t>https://legiscan.com/OR/people/ed-diehl/id/23848</t>
+        </is>
+      </c>
+    </row>
+    <row r="318">
+      <c r="A318" t="inlineStr">
+        <is>
+          <t>David Medina</t>
+        </is>
+      </c>
+      <c r="B318" t="inlineStr">
+        <is>
+          <t>No AI record found</t>
+        </is>
+      </c>
+      <c r="C318" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/David_Medina_(Oregon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="319">
+      <c r="A319" t="inlineStr">
+        <is>
+          <t>Hope Dalrymple</t>
+        </is>
+      </c>
+      <c r="B319" t="inlineStr">
+        <is>
+          <t>No AI record found</t>
+        </is>
+      </c>
+      <c r="C319" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Hope_Dalrymple</t>
+        </is>
+      </c>
+    </row>
+    <row r="320">
+      <c r="A320" t="inlineStr">
+        <is>
+          <t>Kyle Duyck</t>
+        </is>
+      </c>
+      <c r="B320" t="inlineStr">
+        <is>
+          <t>No AI record found</t>
+        </is>
+      </c>
+      <c r="C320" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Kyle_Duyck</t>
+        </is>
+      </c>
+    </row>
+    <row r="321">
+      <c r="A321" t="inlineStr">
+        <is>
+          <t>Forest Alexander</t>
+        </is>
+      </c>
+      <c r="B321" t="inlineStr">
+        <is>
+          <t>No AI record found</t>
+        </is>
+      </c>
+      <c r="C321" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Forest_Alexander</t>
+        </is>
+      </c>
+    </row>
+    <row r="322">
+      <c r="A322" t="inlineStr">
+        <is>
+          <t>James Atkinson</t>
+        </is>
+      </c>
+      <c r="B322" t="inlineStr">
+        <is>
+          <t>No AI record found</t>
+        </is>
+      </c>
+      <c r="C322" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/James_Atkinson_(Oregon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="323">
+      <c r="A323" t="inlineStr">
+        <is>
+          <t>Brittany Jones</t>
+        </is>
+      </c>
+      <c r="B323" t="inlineStr">
+        <is>
+          <t>No AI record found</t>
+        </is>
+      </c>
+      <c r="C323" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Brittany_Jones_(Oregon)</t>
+        </is>
+      </c>
+    </row>
+    <row r="324">
+      <c r="A324" t="inlineStr">
+        <is>
+          <t>Tristan Sheppard</t>
+        </is>
+      </c>
+      <c r="B324" t="inlineStr">
+        <is>
+          <t>No AI record found</t>
+        </is>
+      </c>
+      <c r="C324" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Tristan_Sheppard</t>
+        </is>
+      </c>
+    </row>
+    <row r="325">
+      <c r="A325" t="inlineStr">
+        <is>
+          <t>Ned Lamont</t>
+        </is>
+      </c>
+      <c r="B325" t="inlineStr">
+        <is>
+          <t>Threatened veto of SB 2 in 2024 (comprehensive AI regulation bill covering algorithmic accountability and bias audits), causing House to kill it; threatened veto again in 2025 when revised SB 2 passed Senate 32-4; stated concern about "patchwork quilt of regulations" stifling AI development</t>
+        </is>
+      </c>
+      <c r="C325" t="inlineStr">
+        <is>
+          <t>https://fortune.com/2024/05/09/connecticut-ai-law-veto-threat-lamont-us-ai-regulation/</t>
+        </is>
+      </c>
+    </row>
+    <row r="326">
+      <c r="A326" t="inlineStr">
+        <is>
+          <t>Ned Lamont</t>
+        </is>
+      </c>
+      <c r="B326" t="inlineStr">
+        <is>
+          <t>Proposed own narrower SB 86 (2026): AI companion chatbot safety protocols for mental health distress, hourly reminders of AI identity, and AI regulatory sandbox for insurance/finance/healthcare; also signed deepfake criminalization bill and launched Tech Talent Accelerator 3.0 with 7 colleges and 12 business partners</t>
+        </is>
+      </c>
+      <c r="C326" t="inlineStr">
+        <is>
+          <t>https://hartfordbusiness.com/article/lamont-proposes-bill-to-protect-kids-from-ai-chatbots-create-ai-development-sandbox/</t>
+        </is>
+      </c>
+    </row>
+    <row r="327">
+      <c r="A327" t="inlineStr">
+        <is>
+          <t>Ryan Fazio</t>
+        </is>
+      </c>
+      <c r="B327" t="inlineStr">
+        <is>
+          <t>Cast one of only 4 "no" votes (out of 36) against SB 2 in Connecticut Senate (May 2025) — bipartisan bill that included deepfake criminalization, algorithmic discrimination protections, and AI transparency requirements; serves as Ranking Member of Energy &amp; Technology Committee</t>
+        </is>
+      </c>
+      <c r="C327" t="inlineStr">
+        <is>
+          <t>https://ctnewsjunkie.com/2025/05/15/connecticut-senate-votes-to-regulate-ai-expand-data-privacy/</t>
+        </is>
+      </c>
+    </row>
+    <row r="328">
+      <c r="A328" t="inlineStr">
+        <is>
+          <t>Ryan Fazio</t>
+        </is>
+      </c>
+      <c r="B328" t="inlineStr">
+        <is>
+          <t>No AI safety positions or alternative AI governance proposals found; campaign focused on cutting electric rates, lowering taxes, property tax caps; no AI policy on campaign website</t>
+        </is>
+      </c>
+      <c r="C328" t="inlineStr">
+        <is>
+          <t>https://ryanfazio.com/meet-ryan/</t>
+        </is>
+      </c>
+    </row>
+    <row r="329">
+      <c r="A329" t="inlineStr">
+        <is>
+          <t>Joshua Elliott</t>
+        </is>
+      </c>
+      <c r="B329" t="inlineStr">
+        <is>
+          <t>No AI record found; progressive Democratic state rep challenger</t>
+        </is>
+      </c>
+      <c r="C329" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Connecticut_gubernatorial_and_lieutenant_gubernatorial_election,_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="330">
+      <c r="A330" t="inlineStr">
+        <is>
+          <t>Betsy McCaughey</t>
+        </is>
+      </c>
+      <c r="B330" t="inlineStr">
+        <is>
+          <t>No AI record found; conservative commentator and former NY Lt. Governor; entered race January 2026</t>
+        </is>
+      </c>
+      <c r="C330" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Connecticut_gubernatorial_and_lieutenant_gubernatorial_election,_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="331">
+      <c r="A331" t="inlineStr">
+        <is>
+          <t>Timothy Wilcox</t>
+        </is>
+      </c>
+      <c r="B331" t="inlineStr">
+        <is>
+          <t>No AI record found; minimal polling support</t>
+        </is>
+      </c>
+      <c r="C331" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Connecticut_gubernatorial_and_lieutenant_gubernatorial_election,_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="332">
+      <c r="A332" t="inlineStr">
+        <is>
+          <t>Erin Stewart</t>
+        </is>
+      </c>
+      <c r="B332" t="inlineStr">
+        <is>
+          <t>No AI positions found; 12-year Mayor of New Britain (2013-2025); tech record limited to SMART City municipal infrastructure (solar, EVs, Wi-Fi, traffic lights); no statements on CT SB 2 AI regulation debate; campaign focused on taxes, housing repeal, school choice</t>
+        </is>
+      </c>
+      <c r="C332" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Erin_Stewart</t>
+        </is>
+      </c>
+    </row>
+    <row r="333">
+      <c r="A333" t="inlineStr">
+        <is>
+          <t>Kelly Ayotte</t>
+        </is>
+      </c>
+      <c r="B333" t="inlineStr">
+        <is>
+          <t>Signed HB 143 (2025): private right of action against AI chatbot operators who encourage children toward self-harm, suicide, sexual conduct, or drug use; minimum $1,000 damages per violation</t>
+        </is>
+      </c>
+      <c r="C333" t="inlineStr">
+        <is>
+          <t>https://www.citizenscount.org/bills/hb-143-2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="334">
+      <c r="A334" t="inlineStr">
+        <is>
+          <t>Kelly Ayotte</t>
+        </is>
+      </c>
+      <c r="B334" t="inlineStr">
+        <is>
+          <t>Operates under HB 1688 (2024, signed by Sununu): bans state agencies from using AI to manipulate or surveil public, prohibits real-time biometric/facial recognition without warrant; COGE report (Dec 2025) recommends state embrace AI for efficiency with human oversight required for irreversible decisions</t>
+        </is>
+      </c>
+      <c r="C334" t="inlineStr">
+        <is>
+          <t>https://www.akingump.com/en/insights/ai-law-and-regulation-tracker/new-hampshire-imposes-new-regulations-on-ai-and-criminalizes-deepfakes</t>
+        </is>
+      </c>
+    </row>
+    <row r="335">
+      <c r="A335" t="inlineStr">
+        <is>
+          <t>Cinde Warmington</t>
+        </is>
+      </c>
+      <c r="B335" t="inlineStr">
+        <is>
+          <t>No AI positions found; 2026 campaign centered on affordability, housing, healthcare, opposing Medicaid cuts; no AI statements found across campaign site, NHPR, Ballotpedia, or Concord Monitor coverage</t>
+        </is>
+      </c>
+      <c r="C335" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Cinde_Warmington</t>
+        </is>
+      </c>
+    </row>
+    <row r="336">
+      <c r="A336" t="inlineStr">
+        <is>
+          <t>Corey Lewandowski</t>
+        </is>
+      </c>
+      <c r="B336" t="inlineStr">
+        <is>
+          <t>No AI record found; DHS role covered in contracting controversies but no AI policy involvement documented</t>
+        </is>
+      </c>
+      <c r="C336" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Corey_Lewandowski</t>
+        </is>
+      </c>
+    </row>
+    <row r="337">
+      <c r="A337" t="inlineStr">
+        <is>
+          <t>Jonathan Kiper</t>
+        </is>
+      </c>
+      <c r="B337" t="inlineStr">
+        <is>
+          <t>Used ChatGPT to draft pro se lawsuit arguing NH lawmakers are unconstitutionally underpaid; framed AI as way to "democratize the judicial system"; lawsuit dismissed Mar 2026 — AI adopter framing with no regulatory policy stance</t>
+        </is>
+      </c>
+      <c r="C337" t="inlineStr">
+        <is>
+          <t>https://www.bostonglobe.com/2026/01/23/metro/nh-kiper-ai-lawsuit-unprecedented/</t>
+        </is>
+      </c>
+    </row>
+    <row r="338">
+      <c r="A338" t="inlineStr">
+        <is>
+          <t>Tom Sherman</t>
+        </is>
+      </c>
+      <c r="B338" t="inlineStr">
+        <is>
+          <t>No AI record found; physician-politician focused on healthcare and education; has not formally declared 2026 candidacy</t>
+        </is>
+      </c>
+      <c r="C338" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Tom_Sherman</t>
+        </is>
+      </c>
+    </row>
+    <row r="339">
+      <c r="A339" t="inlineStr">
+        <is>
+          <t>Deaglan McEachern</t>
+        </is>
+      </c>
+      <c r="B339" t="inlineStr">
+        <is>
+          <t>No AI record found; works at Smarsh (communications compliance tech) but no public AI policy positions; campaign focused on housing and transparency</t>
+        </is>
+      </c>
+      <c r="C339" t="inlineStr">
+        <is>
+          <t>https://www.citizenscount.org/candidate/deaglan-mceachern</t>
+        </is>
+      </c>
+    </row>
+    <row r="340">
+      <c r="A340" t="inlineStr">
+        <is>
+          <t>Donovan Fenton</t>
+        </is>
+      </c>
+      <c r="B340" t="inlineStr">
+        <is>
+          <t>No AI record found; 276 bills reviewed via TrackBill with zero AI-related; sits on Commerce committee but uninvolved in NH AI legislation (HB 1432, HB 1688, SB 564)</t>
+        </is>
+      </c>
+      <c r="C340" t="inlineStr">
+        <is>
+          <t>https://trackbill.com/legislator/new-hampshire-senator-donovan-fenton/1088-14739/</t>
+        </is>
+      </c>
+    </row>
+    <row r="341">
+      <c r="A341" t="inlineStr">
+        <is>
+          <t>Jeff Colyer</t>
+        </is>
+      </c>
+      <c r="B341" t="inlineStr">
+        <is>
+          <t>Stated kids need to "know how to code and how to use AI" for jobs of the future; frames AI purely as workforce/economic competitiveness tool; no AI safety, regulation, or accountability positions found</t>
+        </is>
+      </c>
+      <c r="C341" t="inlineStr">
+        <is>
+          <t>https://kansasreflector.com/2026/02/23/republican-candidate-for-kansas-governor-offering-voters-a-prescription-for-change/</t>
+        </is>
+      </c>
+    </row>
+    <row r="342">
+      <c r="A342" t="inlineStr">
+        <is>
+          <t>Jeff Colyer</t>
+        </is>
+      </c>
+      <c r="B342" t="inlineStr">
+        <is>
+          <t>No AI legislation sponsored; former governor 2018-2019 predates major AI policy era; no AI PAC funding found; campaign focused on taxes and tech job attraction</t>
+        </is>
+      </c>
+      <c r="C342" t="inlineStr">
+        <is>
+          <t>https://www.kcur.org/politics-elections-and-government/2025-07-24/kansas-governor-race-2026-election-candidates</t>
+        </is>
+      </c>
+    </row>
+    <row r="343">
+      <c r="A343" t="inlineStr">
+        <is>
+          <t>Ty Masterson</t>
+        </is>
+      </c>
+      <c r="B343" t="inlineStr">
+        <is>
+          <t>No AI record found despite serving as Kansas Senate President during active AI legislation (HB 2592 task force, SB 405, HB 2183 deepfakes); campaign focused on taxes, school choice, anti-DEI, abortion</t>
+        </is>
+      </c>
+      <c r="C343" t="inlineStr">
+        <is>
+          <t>https://kansasreflector.com/2025/07/20/kansas-senate-president-ty-masterson-launches-republican-campaign-for-governor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="344">
+      <c r="A344" t="inlineStr">
+        <is>
+          <t>Cindy Holscher</t>
+        </is>
+      </c>
+      <c r="B344" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on education funding, healthcare, reproductive rights, Medicaid expansion; Ranking Member on Government Efficiency Committee but no AI bills sponsored</t>
+        </is>
+      </c>
+      <c r="C344" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Cindy_Holscher</t>
+        </is>
+      </c>
+    </row>
+    <row r="345">
+      <c r="A345" t="inlineStr">
+        <is>
+          <t>Ethan Corson</t>
+        </is>
+      </c>
+      <c r="B345" t="inlineStr">
+        <is>
+          <t>No AI record found; fundraising leader endorsed by Gov. Kelly and Gov. Sebelius; campaign focused on school funding, middle-class tax cuts, food sales tax elimination</t>
+        </is>
+      </c>
+      <c r="C345" t="inlineStr">
+        <is>
+          <t>https://kansasreflector.com/2025/07/22/kansas-sen-ethan-corson-enters-race-for-democratic-partys-nomination-for-governor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="346">
+      <c r="A346" t="inlineStr">
+        <is>
+          <t>Scott Schwab</t>
+        </is>
+      </c>
+      <c r="B346" t="inlineStr">
+        <is>
+          <t>Co-authored Jan 2024 Foreign Affairs article "Artificial Intelligence's Threat to Democracy" with CISA Director Jen Easterly; warned AI deepfakes and voice-cloning lower barrier for election misinformation; framed as national security/election integrity concern, not regulatory legislation</t>
+        </is>
+      </c>
+      <c r="C346" t="inlineStr">
+        <is>
+          <t>https://www.foreignaffairs.com/united-states/artificial-intelligences-threat-democracy</t>
+        </is>
+      </c>
+    </row>
+    <row r="347">
+      <c r="A347" t="inlineStr">
+        <is>
+          <t>Vicki Schmidt</t>
+        </is>
+      </c>
+      <c r="B347" t="inlineStr">
+        <is>
+          <t>No personal AI record found; NAIC Midwest Zone Chair (2024) on committees working on AI insurance regulation but Kansas has not adopted NAIC Model Bulletin on AI Use by Insurers; no AI campaign statements</t>
+        </is>
+      </c>
+      <c r="C347" t="inlineStr">
+        <is>
+          <t>https://kansasreflector.com/2025/07/21/kansas-republican-vicki-schmidt-anchors-2026-campaign-for-governor-on-record-of-service/</t>
+        </is>
+      </c>
+    </row>
+    <row r="348">
+      <c r="A348" t="inlineStr">
+        <is>
+          <t>Charlotte O'Hara</t>
+        </is>
+      </c>
+      <c r="B348" t="inlineStr">
+        <is>
+          <t>No AI record found; left Johnson County Commission Jan 2025 before county AI policy work began; no AI positions as state House member (2011-2013) or as governor candidate</t>
+        </is>
+      </c>
+      <c r="C348" t="inlineStr">
+        <is>
+          <t>https://oharaforkansas.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="349">
+      <c r="A349" t="inlineStr">
+        <is>
+          <t>Stacy Rogers</t>
+        </is>
+      </c>
+      <c r="B349" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on jobs, taxes, parental rights</t>
+        </is>
+      </c>
+      <c r="C349" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Stacy_Rogers</t>
+        </is>
+      </c>
+    </row>
+    <row r="350">
+      <c r="A350" t="inlineStr">
+        <is>
+          <t>Philip Sarnecki</t>
+        </is>
+      </c>
+      <c r="B350" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign funded by $2M personal loan; focused on jobs, lower taxes, parental rights, reducing red tape</t>
+        </is>
+      </c>
+      <c r="C350" t="inlineStr">
+        <is>
+          <t>https://philipsarnecki.org/about/</t>
+        </is>
+      </c>
+    </row>
+    <row r="351">
+      <c r="A351" t="inlineStr">
+        <is>
+          <t>Marty Tuley</t>
+        </is>
+      </c>
+      <c r="B351" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on teacher pay, school meals, cannabis legalization for education funding, rural Kansas; no AI mention in March 2026 Dem debate</t>
+        </is>
+      </c>
+      <c r="C351" t="inlineStr">
+        <is>
+          <t>https://www.tuley4gov2026.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="352">
+      <c r="A352" t="inlineStr">
+        <is>
+          <t>Deb Haaland</t>
+        </is>
+      </c>
+      <c r="B352" t="inlineStr">
+        <is>
+          <t>Pledged to ban algorithmic rent-fixing (AI software used by landlords to dynamically adjust lease prices) as part of Feb 2026 affordability agenda; framed as protecting renters from corporations using "AI programs to change the cost of a monthly lease on a regular basis"</t>
+        </is>
+      </c>
+      <c r="C352" t="inlineStr">
+        <is>
+          <t>https://sourcenm.com/2026/02/25/deb-haaland-announces-affordability-agenda-in-campaign-for-nm-governor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="353">
+      <c r="A353" t="inlineStr">
+        <is>
+          <t>Deb Haaland</t>
+        </is>
+      </c>
+      <c r="B353" t="inlineStr">
+        <is>
+          <t>No AI bills sponsored in House (2019-2021); not a co-sponsor of Algorithmic Accountability Act of 2019; no AI-specific initiatives as Interior Secretary; campaign funded by 51,000 small-dollar donors with no AI PAC backing</t>
+        </is>
+      </c>
+      <c r="C353" t="inlineStr">
+        <is>
+          <t>https://www.govtrack.us/congress/members/debra_haaland/412800</t>
+        </is>
+      </c>
+    </row>
+    <row r="354">
+      <c r="A354" t="inlineStr">
+        <is>
+          <t>Gregg Hull</t>
+        </is>
+      </c>
+      <c r="B354" t="inlineStr">
+        <is>
+          <t>No AI record found; tech-adjacent record limited to championing Intel semiconductor expansion in Rio Rancho ($500M, 700 jobs); no statements on NM AI legislation (HB 60, AG Torrez deepfake proposal)</t>
+        </is>
+      </c>
+      <c r="C354" t="inlineStr">
+        <is>
+          <t>https://gregghull.com/issues/</t>
+        </is>
+      </c>
+    </row>
+    <row r="355">
+      <c r="A355" t="inlineStr">
+        <is>
+          <t>Sam Bregman</t>
+        </is>
+      </c>
+      <c r="B355" t="inlineStr">
+        <is>
+          <t>Explicitly supports attracting AI data centers and quantum computing to NM as economic priority; stated "I'm all for high tech. That is a huge part of our future"; frames oil/gas as bridge to power AI data center infrastructure; no AI regulation, deepfake, or safety positions found</t>
+        </is>
+      </c>
+      <c r="C355" t="inlineStr">
+        <is>
+          <t>https://sandovalsignpost.com/2025/11/bregman-touts-high-tech-future-for-sandoval-county/</t>
+        </is>
+      </c>
+    </row>
+    <row r="356">
+      <c r="A356" t="inlineStr">
+        <is>
+          <t>Ken Miyagishima</t>
+        </is>
+      </c>
+      <c r="B356" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on crime (cash bail), doctor shortages, housing, water policy (geothermal desalination), tax reform</t>
+        </is>
+      </c>
+      <c r="C356" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Ken_Miyagishima</t>
+        </is>
+      </c>
+    </row>
+    <row r="357">
+      <c r="A357" t="inlineStr">
+        <is>
+          <t>Duke Rodriguez</t>
+        </is>
+      </c>
+      <c r="B357" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on guaranteed healthcare, education reform, crime, homelessness, public pension protection</t>
+        </is>
+      </c>
+      <c r="C357" t="inlineStr">
+        <is>
+          <t>https://runwithduke.com/priorities/</t>
+        </is>
+      </c>
+    </row>
+    <row r="358">
+      <c r="A358" t="inlineStr">
+        <is>
+          <t>Steve Lanier</t>
+        </is>
+      </c>
+      <c r="B358" t="inlineStr">
+        <is>
+          <t>No AI record found; legislative record focuses on education, rural NM, voter ID, swatting felony bill</t>
+        </is>
+      </c>
+      <c r="C358" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Steve_Lanier</t>
+        </is>
+      </c>
+    </row>
+    <row r="359">
+      <c r="A359" t="inlineStr">
+        <is>
+          <t>Doug Turner</t>
+        </is>
+      </c>
+      <c r="B359" t="inlineStr">
+        <is>
+          <t>No AI record found; op-ed touches on "modern technology" only in law enforcement context; no AI-specific positions in campaign materials</t>
+        </is>
+      </c>
+      <c r="C359" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Doug_Turner_(New_Mexico)</t>
+        </is>
+      </c>
+    </row>
+    <row r="360">
+      <c r="A360" t="inlineStr">
+        <is>
+          <t>Randy Feenstra</t>
+        </is>
+      </c>
+      <c r="B360" t="inlineStr">
+        <is>
+          <t>Led Farm Tech Act (H.R. 6806, Dec 2023): bipartisan bill requiring USDA certification program for agricultural AI software based on NIST AI Risk Management Framework, to "protect farmers from faulty or misleading technologies"; voted YES on TAKE IT DOWN Act (federal deepfake porn ban), stating "we must do a better job of removing these false depictions online"</t>
+        </is>
+      </c>
+      <c r="C360" t="inlineStr">
+        <is>
+          <t>https://feenstra.house.gov/media/press-releases/feenstra-leads-legislation-certify-efficacy-legitimacy-and-safety-farm</t>
+        </is>
+      </c>
+    </row>
+    <row r="361">
+      <c r="A361" t="inlineStr">
+        <is>
+          <t>Randy Feenstra</t>
+        </is>
+      </c>
+      <c r="B361" t="inlineStr">
+        <is>
+          <t>Delivered opening statement at House Science Subcommittee hearing on "Trustworthy AI: Managing the Risks of Artificial Intelligence" (Sept 2022); on campaign trail said AI offers "huge opportunities" but "there's gotta be guardrails in making sure it's safe"; no broader algorithmic accountability or consumer AI regulation positions found</t>
+        </is>
+      </c>
+      <c r="C361" t="inlineStr">
+        <is>
+          <t>https://www.newtondailynews.com/article/788,randy-feenstra-says-ai-offers-huge-opportunities-nuclear-is-way-of-the-future</t>
+        </is>
+      </c>
+    </row>
+    <row r="362">
+      <c r="A362" t="inlineStr">
+        <is>
+          <t>Rob Sand</t>
+        </is>
+      </c>
+      <c r="B362" t="inlineStr">
+        <is>
+          <t>Uses AI tools internally at State Auditor office for efficiency ("two programs that trim a substantial number of hours off our work"); frames AI as augmenting not replacing workers; no public statements on AI regulation, safety, deepfakes, or workforce impacts; no AI plank on campaign site</t>
+        </is>
+      </c>
+      <c r="C362" t="inlineStr">
+        <is>
+          <t>https://www.workiva.com/resources/rob-sand-iowa-state-auditor-efficiency-aficionado</t>
+        </is>
+      </c>
+    </row>
+    <row r="363">
+      <c r="A363" t="inlineStr">
+        <is>
+          <t>Eddie Andrews</t>
+        </is>
+      </c>
+      <c r="B363" t="inlineStr">
+        <is>
+          <t>No AI positions found; sits on House Economic Growth and Technology Committee which advanced AI deepfakes bill HSB294 (18-3, Mar 2025) but was not a sponsor; campaign focused on education, property taxes, mental health</t>
+        </is>
+      </c>
+      <c r="C363" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Eddie_Andrews</t>
+        </is>
+      </c>
+    </row>
+    <row r="364">
+      <c r="A364" t="inlineStr">
+        <is>
+          <t>Zach Lahn</t>
+        </is>
+      </c>
+      <c r="B364" t="inlineStr">
+        <is>
+          <t>Opposes Iowa data center tax incentives (Feb 2026): proposes charging AI data centers 5x standard property tax rate; criticized half-billion-dollar rebate to QTS for only 30 jobs; told companies threatening to leave "Yes. Go." — populist/skeptical of corporate AI buildout, not an AI safety or regulation position</t>
+        </is>
+      </c>
+      <c r="C364" t="inlineStr">
+        <is>
+          <t>https://www.radioiowa.com/2026/02/19/lahn-pledges-as-iowa-governor-hed-change-policy-on-data-centers/</t>
+        </is>
+      </c>
+    </row>
+    <row r="365">
+      <c r="A365" t="inlineStr">
+        <is>
+          <t>Brad Sherman</t>
+        </is>
+      </c>
+      <c r="B365" t="inlineStr">
+        <is>
+          <t>Cautioned that "while AI can be a useful tool, students should not rely on it too heavily" as it weakens foundational thinking skills; paired with opposition to calculator reliance in education — mild cautionary statement, not a regulatory or policy position</t>
+        </is>
+      </c>
+      <c r="C365" t="inlineStr">
+        <is>
+          <t>https://www.thenews-ia.com/stories/restoring-the-foundations-of-freedom-why-brad-sherman-is-running-for-iowa-governor,170840</t>
+        </is>
+      </c>
+    </row>
+    <row r="366">
+      <c r="A366" t="inlineStr">
+        <is>
+          <t>Adam Steen</t>
+        </is>
+      </c>
+      <c r="B366" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on faith, property rights, school choice, trades education, administrative experience</t>
+        </is>
+      </c>
+      <c r="C366" t="inlineStr">
+        <is>
+          <t>https://iowacapitaldispatch.com/2025/08/19/former-iowa-administrator-adam-steen-announces-gop-campaign-for-governor/</t>
+        </is>
+      </c>
+    </row>
+    <row r="367">
+      <c r="A367" t="inlineStr">
+        <is>
+          <t>Julie Stauch</t>
+        </is>
+      </c>
+      <c r="B367" t="inlineStr">
+        <is>
+          <t>No AI record found; priorities are water quality, public school funding, healthcare access, eminent domain</t>
+        </is>
+      </c>
+      <c r="C367" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Julie_Stauch</t>
+        </is>
+      </c>
+    </row>
+    <row r="368">
+      <c r="A368" t="inlineStr">
+        <is>
+          <t>Paul Dahl</t>
+        </is>
+      </c>
+      <c r="B368" t="inlineStr">
+        <is>
+          <t>No AI record found; platform focuses on agricultural reform, circular economy, infrastructure, education</t>
+        </is>
+      </c>
+      <c r="C368" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Paul_Dahl</t>
+        </is>
+      </c>
+    </row>
+    <row r="369">
+      <c r="A369" t="inlineStr">
+        <is>
+          <t>Nirav Shah</t>
+        </is>
+      </c>
+      <c r="B369" t="inlineStr">
+        <is>
+          <t>No AI record found; former Maine CDC director and CDC Principal Deputy Director oversaw data modernization but made no AI policy statements; campaign focused on housing, food insecurity, healthcare, economic growth</t>
+        </is>
+      </c>
+      <c r="C369" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Nirav_Shah</t>
+        </is>
+      </c>
+    </row>
+    <row r="370">
+      <c r="A370" t="inlineStr">
+        <is>
+          <t>Bobby Charles</t>
+        </is>
+      </c>
+      <c r="B370" t="inlineStr">
+        <is>
+          <t>No AI policy positions found; uses AI-generated imagery in campaign social media without commenting on AI policy; general deregulatory stance ("slash unnecessary regulation") but no AI-specific statement; former Naval Intelligence Officer and Asst. Secretary of State</t>
+        </is>
+      </c>
+      <c r="C370" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Bobby_Charles</t>
+        </is>
+      </c>
+    </row>
+    <row r="371">
+      <c r="A371" t="inlineStr">
+        <is>
+          <t>Hannah Pingree</t>
+        </is>
+      </c>
+      <c r="B371" t="inlineStr">
+        <is>
+          <t>Served as Director of Governor Mills Office of Policy Innovation and the Future (2019-May 2025), administratively overseeing Maine AI Task Force (created Dec 2024 exec order); framed AI as holding "tremendous promise" while calling for ensuring benefits reach Maine people and "minimizing disruptions"; task force produced 33 recommendations on workforce, procurement transparency, and privacy</t>
+        </is>
+      </c>
+      <c r="C371" t="inlineStr">
+        <is>
+          <t>https://www1.maine.gov/governor/mills/news/governor-mills-signs-executive-order-establishing-task-force-artificial-intelligence-2024-12</t>
+        </is>
+      </c>
+    </row>
+    <row r="372">
+      <c r="A372" t="inlineStr">
+        <is>
+          <t>Shenna Bellows</t>
+        </is>
+      </c>
+      <c r="B372" t="inlineStr">
+        <is>
+          <t>As Secretary of State, submitted testimony supporting Maine deepfake political ad disclosure bill (LD 517); stated AI will "supercharge" voter fears about what is true and false; bill advanced Maine House 73-65 (Mar 2026), would make Maine 27th state to regulate AI in political ads</t>
+        </is>
+      </c>
+      <c r="C372" t="inlineStr">
+        <is>
+          <t>https://www.mainepublic.org/politics/2025-04-28/bill-would-require-disclosure-of-deepfake-political-ads</t>
+        </is>
+      </c>
+    </row>
+    <row r="373">
+      <c r="A373" t="inlineStr">
+        <is>
+          <t>Eloise Vitelli</t>
+        </is>
+      </c>
+      <c r="B373" t="inlineStr">
+        <is>
+          <t>As Senate Majority Leader, was among 5 Democrats on Legislative Council who voted 5-5 (Oct 2025) to block AI-generated CSAM bill (LR-2652) from reaching committee; stated existing LD 1944 already covered it, but reporting confirmed protective provisions had been stripped from LD 1944 before signing; has prior record sponsoring child-protection legislation</t>
+        </is>
+      </c>
+      <c r="C373" t="inlineStr">
+        <is>
+          <t>https://www.themainewire.com/2025/10/maine-democrats-vote-down-proposed-bill-to-ban-ai-child-porn/</t>
+        </is>
+      </c>
+    </row>
+    <row r="374">
+      <c r="A374" t="inlineStr">
+        <is>
+          <t>Angus King III</t>
+        </is>
+      </c>
+      <c r="B374" t="inlineStr">
+        <is>
+          <t>Mentioned AI for grid efficiency and stated AI data centers "are going to have to bring their own power" to protect ratepayers; no AI governance, safety, or regulation positions found; background is renewable energy entrepreneurship</t>
+        </is>
+      </c>
+      <c r="C374" t="inlineStr">
+        <is>
+          <t>https://angusforgovernor.com/angus-king-iii-unveils-energy-ratepayer-bill-of-rights-to-lower-costs-improve-reliability-and-deliver-a-fair-deal-for-maine-families/</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" t="inlineStr">
+        <is>
+          <t>Troy Jackson</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on working families, labor rights, rural healthcare; signed People's Pledge rejecting corporate PACs; no comment on Maine AI Task Force or LD 517</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>https://jacksonformaine.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" t="inlineStr">
+        <is>
+          <t>Owen McCarthy</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>Co-founded MedRhythms (AI + neuroscience to restore mobility in stroke/Parkinson's patients; FDA-cleared, $60M+ raised); frames AI as economic opportunity for rural Maine; aligned with Trump "AI dominance" posture; no positions on AI safety, deepfakes, or algorithmic accountability</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>https://owenformaine.com/why/</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" t="inlineStr">
+        <is>
+          <t>James Libby</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>Appointed to Gov. Mills Maine AI Task Force (Dec 2024 exec order) by Senate President Daughtry; task force issued 33 recommendations Oct 2025; campaign platform explicitly includes "Utilize AI in Government Operations and HR to Economize" — frames AI as efficiency tool to reduce government size; no safety or consumer protection positions</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>https://www.jimlibbyforgovernor.com/good-government</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" t="inlineStr">
+        <is>
+          <t>Garrett Mason</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>No AI record found; former Senate Majority Leader and lobbyist; campaign focused on crime, taxation, legislative experience; no AI platform, no AI lobbying clients found</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Garrett_Mason</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" t="inlineStr">
+        <is>
+          <t>Jonathan Bush</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>No AI campaign positions found; health tech entrepreneur background (athenahealth, Zus Health) and attended AI Health Conference 2026 professionally; campaign focused on economic growth, tax cuts, deregulation</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>https://jonathanbush.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" t="inlineStr">
+        <is>
+          <t>Ben Midgley</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on housing, energy costs, crime, parental rights</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Ben_Midgley</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" t="inlineStr">
+        <is>
+          <t>David Jones</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>No AI record found; campaign focused on taxes, regulation, economic growth</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/David_Jones_(Maine_gubernatorial_candidate)</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" t="inlineStr">
+        <is>
+          <t>Robert Wessels</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>No AI record found; generic "leverage technology to create efficiencies" language on platform; no AI-specific position</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>https://www.voterobertwessels.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="383">
+      <c r="A383" t="inlineStr">
+        <is>
+          <t>Kenneth Capron</t>
+        </is>
+      </c>
+      <c r="B383" t="inlineStr">
+        <is>
+          <t>No AI record found; retired CPA and systems engineer (Y2K background) but no AI campaign stance documented</t>
+        </is>
+      </c>
+      <c r="C383" t="inlineStr">
+        <is>
+          <t>https://www.newscentermaine.com/article/news/politics/maine-politics/ken-capron-run-for-governor-maine-republican-portland/97-a4e58125-4170-4cd3-a9fc-41714371e842</t>
+        </is>
+      </c>
+    </row>
+    <row r="384">
+      <c r="A384" t="inlineStr">
+        <is>
+          <t>Derek Levasseur</t>
+        </is>
+      </c>
+      <c r="B384" t="inlineStr">
+        <is>
+          <t>No AI record found; former law enforcement; campaign focused on cost of living, property tax elimination, DHHS reform</t>
+        </is>
+      </c>
+      <c r="C384" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Derek_Levasseur</t>
+        </is>
+      </c>
+    </row>
+    <row r="385">
+      <c r="A385" t="inlineStr">
+        <is>
+          <t>Alexander Murchison</t>
+        </is>
+      </c>
+      <c r="B385" t="inlineStr">
+        <is>
+          <t>No AI record found; generic "leaving room for advancement in technology" language only</t>
+        </is>
+      </c>
+      <c r="C385" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Maine_gubernatorial_election,_2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="386">
+      <c r="A386" t="inlineStr">
+        <is>
+          <t>Richard Bennett</t>
+        </is>
+      </c>
+      <c r="B386" t="inlineStr">
+        <is>
+          <t>No AI record found; former Republican Maine Senate President; campaign focused on fiscal responsibility, education, housing, rural healthcare; championed ranked-choice voting and dark money reform</t>
+        </is>
+      </c>
+      <c r="C386" t="inlineStr">
+        <is>
+          <t>https://bennettforgovernor.com</t>
+        </is>
+      </c>
+    </row>
+    <row r="387">
+      <c r="A387" t="inlineStr">
+        <is>
+          <t>W. Edward Crockett</t>
+        </is>
+      </c>
+      <c r="B387" t="inlineStr">
+        <is>
+          <t>No AI record found; former Democratic state rep; running as clean elections candidate; no AI position despite serving during passage of Maine AI transparency law</t>
+        </is>
+      </c>
+      <c r="C387" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/W._Edward_Crockett</t>
+        </is>
+      </c>
+    </row>
+    <row r="388">
+      <c r="A388" t="inlineStr">
+        <is>
+          <t>John Glowa</t>
+        </is>
+      </c>
+      <c r="B388" t="inlineStr">
+        <is>
+          <t>No AI record found; retired environmental specialist; campaign focused on structural political reform and environmental advocacy</t>
+        </is>
+      </c>
+      <c r="C388" t="inlineStr">
+        <is>
+          <t>https://johnglowaforgovernor.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="389">
+      <c r="A389" t="inlineStr">
+        <is>
+          <t>Cory Booker</t>
+        </is>
+      </c>
+      <c r="B389" t="inlineStr">
+        <is>
+          <t>Co-lead of Algorithmic Accountability Act (2023 and 2025 versions): requires companies to conduct impact assessments on AI systems making high-stakes decisions in housing/employment/education/credit; creates FTC public database; adds 75 FTC staff for enforcement</t>
+        </is>
+      </c>
+      <c r="C389" t="inlineStr">
+        <is>
+          <t>https://www.booker.senate.gov/news/press/booker-wyden-clarke-introduce-bicameral-bill-to-regulate-use-of-artificial-intelligence-to-make-critical-decisions-like-housing-employment-and-education</t>
+        </is>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>Cory Booker</t>
+        </is>
+      </c>
+      <c r="B390" t="inlineStr">
+        <is>
+          <t>Co-sponsored bipartisan CREATE AI Act to establish National AI Research Resource (NAIRR) providing researchers and students shared access to AI data and compute infrastructure — pro-innovation posture</t>
+        </is>
+      </c>
+      <c r="C390" t="inlineStr">
+        <is>
+          <t>https://x.com/SenBooker/status/1692270712914870704</t>
+        </is>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>Cory Booker</t>
+        </is>
+      </c>
+      <c r="B391" t="inlineStr">
+        <is>
+          <t>Highlighted civil rights concerns about biased AI in hiring and healthcare: 'I love technology and innovation' but 'technology can elevate the power of discrimination'; also introduced bipartisan AI Grand Challenges Act to use AI for health/energy/national security</t>
+        </is>
+      </c>
+      <c r="C391" t="inlineStr">
+        <is>
+          <t>https://thehill.com/homenews/race-politics/4228791-booker-experts-highlight-civil-rights-concerns-in-artificial-intelligence/</t>
+        </is>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>Cory Booker</t>
+        </is>
+      </c>
+      <c r="B392" t="inlineStr">
+        <is>
+          <t>Co-sponsor of AI Civil Rights Act (2025) with Markey and Warren — bans discriminatory AI in critical decisions and requires pre/post-deployment testing</t>
+        </is>
+      </c>
+      <c r="C392" t="inlineStr">
+        <is>
+          <t>https://www.nextgov.com/artificial-intelligence/2025/12/democrats-bring-back-ai-civil-rights-bill/409869/</t>
+        </is>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>Alex Zdan</t>
+        </is>
+      </c>
+      <c r="B393" t="inlineStr">
+        <is>
+          <t>No AI-specific policy positions found; campaign website focuses on Big Tech antitrust ('break their stranglehold on power') and content moderation concerns but makes no mention of AI regulation or innovation policy</t>
+        </is>
+      </c>
+      <c r="C393" t="inlineStr">
+        <is>
+          <t>https://zdanforsenate.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>Justin Murphy</t>
+        </is>
+      </c>
+      <c r="B394" t="inlineStr">
+        <is>
+          <t>No AI-specific positions found; platform centers on Pinelands conservation / Jersey Shore / parental rights / abolishing Dept. of Education; no AI bills sponsored in prior legislative activity</t>
+        </is>
+      </c>
+      <c r="C394" t="inlineStr">
+        <is>
+          <t>https://jerseyjustin4senate.org/</t>
+        </is>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>Richard Tabor</t>
+        </is>
+      </c>
+      <c r="B395" t="inlineStr">
+        <is>
+          <t>No AI-specific positions found; state trooper and Army combat veteran; campaign focused on law enforcement and veterans issues; no AI statements identified across campaign materials or news coverage</t>
+        </is>
+      </c>
+      <c r="C395" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Richard_Tabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>Natalie Rivera</t>
+        </is>
+      </c>
+      <c r="B396" t="inlineStr">
+        <is>
+          <t>No AI-specific positions found; perennial Senate candidate (2018 independent / 2020 Republican) with platform on Second Amendment / healthcare / prison reform; no AI or tech policy positions found across campaign sites or Ballotpedia</t>
+        </is>
+      </c>
+      <c r="C396" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Natalie_Rivera</t>
+        </is>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>Robert Lebovics</t>
+        </is>
+      </c>
+      <c r="B397" t="inlineStr">
+        <is>
+          <t>No AI-specific positions found; nationally-known otolaryngologist running as centrist Republican; campaign website and Ballotpedia profile contain no statements on AI or tech innovation</t>
+        </is>
+      </c>
+      <c r="C397" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Robert_Lebovics</t>
+        </is>
+      </c>
+    </row>
+    <row r="398">
+      <c r="A398" t="inlineStr">
+        <is>
+          <t>Andy Barr</t>
+        </is>
+      </c>
+      <c r="B398" t="inlineStr">
+        <is>
+          <t>Barr declares AI 'a national security imperative,' introduces coal/nuclear power bill for AI data centers, opposes state-level regulatory regimes</t>
+        </is>
+      </c>
+      <c r="C398" t="inlineStr">
+        <is>
+          <t>https://www.wpsdlocal6.com/news/rep-andy-barr-talks-nuclear-energy-artificial-intelligence-and-opponents-on-campaign-trail/article_5cf7b36d-70d9-4bba-93e7-76f80e578b71.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="399">
+      <c r="A399" t="inlineStr">
+        <is>
+          <t>Daniel Cameron</t>
+        </is>
+      </c>
+      <c r="B399" t="inlineStr">
+        <is>
+          <t>Wants KY to be 'heart of America's tech revolution' via AI/crypto/robotics but previously urged Congress to study AI's harmful effects on kids; workforce concerns</t>
+        </is>
+      </c>
+      <c r="C399" t="inlineStr">
+        <is>
+          <t>https://www.union-bulletin.com/news/national/kentucky-s-senate-candidates-divided-on-how-to-handle-artificial-intelligence/article_f9402688-0852-58e7-96bd-f793c7e6afd8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="400">
+      <c r="A400" t="inlineStr">
+        <is>
+          <t>Nate Morris</t>
+        </is>
+      </c>
+      <c r="B400" t="inlineStr">
+        <is>
+          <t>Backs Trump AI preemption '100%,' pro-innovation framing, Elon Musk-backed tech outsider candidate</t>
+        </is>
+      </c>
+      <c r="C400" t="inlineStr">
+        <is>
+          <t>https://www.nbcnews.com/politics/2026-election/nate-morris-kentucky-gop-senate-candidate-jd-vance-rcna217872</t>
+        </is>
+      </c>
+    </row>
+    <row r="401">
+      <c r="A401" t="inlineStr">
+        <is>
+          <t>Charles Booker</t>
+        </is>
+      </c>
+      <c r="B401" t="inlineStr">
+        <is>
+          <t>Opposes federal AI preemption, frames AI as labor/equity issue, supports UBI for displaced workers, rejects China-race deregulation framing</t>
+        </is>
+      </c>
+      <c r="C401" t="inlineStr">
+        <is>
+          <t>https://www.union-bulletin.com/news/national/kentucky-s-senate-candidates-divided-on-how-to-handle-artificial-intelligence/article_f9402688-0852-58e7-96bd-f793c7e6afd8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="402">
+      <c r="A402" t="inlineStr">
+        <is>
+          <t>Amy McGrath</t>
+        </is>
+      </c>
+      <c r="B402" t="inlineStr">
+        <is>
+          <t>Says AI growth is 'inevitable' and U.S. must lead, but calls technology 'eye-watering' scary; concerned about national security risks of Trump's chip deals</t>
+        </is>
+      </c>
+      <c r="C402" t="inlineStr">
+        <is>
+          <t>https://www.union-bulletin.com/news/national/kentucky-s-senate-candidates-divided-on-how-to-handle-artificial-intelligence/article_f9402688-0852-58e7-96bd-f793c7e6afd8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="403">
+      <c r="A403" t="inlineStr">
+        <is>
+          <t>Pamela Stevenson</t>
+        </is>
+      </c>
+      <c r="B403" t="inlineStr">
+        <is>
+          <t>Opposes federal preemption of state AI regulation, argues states should have autonomy to set their own AI oversight rules</t>
+        </is>
+      </c>
+      <c r="C403" t="inlineStr">
+        <is>
+          <t>https://www.union-bulletin.com/news/national/kentucky-s-senate-candidates-divided-on-how-to-handle-artificial-intelligence/article_f9402688-0852-58e7-96bd-f793c7e6afd8.html</t>
+        </is>
+      </c>
+    </row>
+    <row r="404">
+      <c r="A404" t="inlineStr">
+        <is>
+          <t>Cory Booker</t>
+        </is>
+      </c>
+      <c r="B404" t="inlineStr">
+        <is>
+          <t>Co-leads Algorithmic Accountability Act (bias audits on high-stakes AI) and AI Civil Rights Act, while also co-sponsoring CREATE AI Act for research infrastructure; targeted regulation on equity grounds, not anti-AI</t>
+        </is>
+      </c>
+      <c r="C404" t="inlineStr">
+        <is>
+          <t>https://www.booker.senate.gov/news/press/booker-wyden-clarke-introduce-bicameral-bill-to-regulate-use-of-artificial-intelligence-to-make-critical-decisions-like-housing-employment-and-education</t>
+        </is>
+      </c>
+    </row>
+    <row r="405">
+      <c r="A405" t="inlineStr">
+        <is>
+          <t>Alex Zdan</t>
+        </is>
+      </c>
+      <c r="B405" t="inlineStr">
+        <is>
+          <t>Former TV reporter; platform focuses on Big Tech antitrust and content moderation, no AI-specific positions</t>
+        </is>
+      </c>
+      <c r="C405" t="inlineStr">
+        <is>
+          <t>https://zdanforsenate.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="406">
+      <c r="A406" t="inlineStr">
+        <is>
+          <t>Justin Murphy</t>
+        </is>
+      </c>
+      <c r="B406" t="inlineStr">
+        <is>
+          <t>Author/attorney/Navy veteran; platform covers parental rights and federal agencies, no AI positions found</t>
+        </is>
+      </c>
+      <c r="C406" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Justin_Murphy_(New_Jersey)</t>
+        </is>
+      </c>
+    </row>
+    <row r="407">
+      <c r="A407" t="inlineStr">
+        <is>
+          <t>Richard Tabor</t>
+        </is>
+      </c>
+      <c r="B407" t="inlineStr">
+        <is>
+          <t>NJ state trooper, Army veteran; campaign entirely focused on law enforcement and veterans issues, no AI statements</t>
+        </is>
+      </c>
+      <c r="C407" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Richard_Tabor</t>
+        </is>
+      </c>
+    </row>
+    <row r="408">
+      <c r="A408" t="inlineStr">
+        <is>
+          <t>Natalie Rivera</t>
+        </is>
+      </c>
+      <c r="B408" t="inlineStr">
+        <is>
+          <t>Third Senate run; platform covers 2A, healthcare, prison reform — no AI or tech positions</t>
+        </is>
+      </c>
+      <c r="C408" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Natalie_Rivera</t>
+        </is>
+      </c>
+    </row>
+    <row r="409">
+      <c r="A409" t="inlineStr">
+        <is>
+          <t>Robert Lebovics</t>
+        </is>
+      </c>
+      <c r="B409" t="inlineStr">
+        <is>
+          <t>Otolaryngologist running as centrist Republican; no AI or tech policy statements found</t>
+        </is>
+      </c>
+      <c r="C409" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Robert_Lebovics</t>
+        </is>
+      </c>
+    </row>
+    <row r="410">
+      <c r="A410" t="inlineStr">
+        <is>
+          <t>Ashley Moody</t>
+        </is>
+      </c>
+      <c r="B410" t="inlineStr">
+        <is>
+          <t>As FL AG, flagged AI voice-cloning as a 'grave new threat' for scam calls; sits on Senate Judiciary Privacy &amp; Technology subcommittee; law-enforcement framing, no sweeping regulatory stance</t>
+        </is>
+      </c>
+      <c r="C410" t="inlineStr">
+        <is>
+          <t>https://www.wusf.org/economy-business/2023-07-20/ashley-moody-ai-making-scam-calls-worse</t>
+        </is>
+      </c>
+    </row>
+    <row r="411">
+      <c r="A411" t="inlineStr">
+        <is>
+          <t>Alex Vindman</t>
+        </is>
+      </c>
+      <c r="B411" t="inlineStr">
+        <is>
+          <t>Campaign focused on cost-of-living, corruption, and anti-Trump; zero AI or tech policy statements in any campaign material</t>
+        </is>
+      </c>
+      <c r="C411" t="inlineStr">
+        <is>
+          <t>https://alexvindman.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="412">
+      <c r="A412" t="inlineStr">
+        <is>
+          <t>Angie Nixon</t>
+        </is>
+      </c>
+      <c r="B412" t="inlineStr">
+        <is>
+          <t>Serves on FL House IT Budget &amp; Policy subcommittee but has made no AI-specific statements in Senate campaign</t>
+        </is>
+      </c>
+      <c r="C412" t="inlineStr">
+        <is>
+          <t>https://angienixon.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="413">
+      <c r="A413" t="inlineStr">
+        <is>
+          <t>Alan Grayson</t>
+        </is>
+      </c>
+      <c r="B413" t="inlineStr">
+        <is>
+          <t>Former House member on Science &amp; Technology Committee (pre-AI era); no AI positions found in 2026 campaign</t>
+        </is>
+      </c>
+      <c r="C413" t="inlineStr">
+        <is>
+          <t>https://ballotpedia.org/Alan_Grayson</t>
         </is>
       </c>
     </row>
@@ -8726,1103 +14377,1306 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C73"/>
+  <dimension ref="A1:D72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
+          <t>Priority</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
           <t>State</t>
         </is>
       </c>
-      <c r="B1" t="inlineStr">
+      <c r="C1" t="inlineStr">
         <is>
           <t>Office</t>
         </is>
       </c>
-      <c r="C1" t="inlineStr">
+      <c r="D1" t="inlineStr">
         <is>
           <t>Completed</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" t="inlineStr">
+      <c r="A2" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" t="inlineStr">
         <is>
           <t>Arizona</t>
         </is>
       </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C2" t="b">
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D2" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" t="inlineStr">
+      <c r="A3" t="n">
+        <v>2</v>
+      </c>
+      <c r="B3" t="inlineStr">
         <is>
           <t>California</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C3" t="b">
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D3" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="4">
-      <c r="A4" t="inlineStr">
+      <c r="A4" t="n">
+        <v>3</v>
+      </c>
+      <c r="B4" t="inlineStr">
         <is>
           <t>Colorado</t>
         </is>
       </c>
-      <c r="B4" t="inlineStr">
+      <c r="C4" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C4" t="b">
+      <c r="D4" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="5">
-      <c r="A5" t="inlineStr">
+      <c r="A5" t="n">
+        <v>4</v>
+      </c>
+      <c r="B5" t="inlineStr">
         <is>
           <t>Florida</t>
         </is>
       </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C5" t="b">
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D5" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" t="inlineStr">
+      <c r="A6" t="n">
+        <v>5</v>
+      </c>
+      <c r="B6" t="inlineStr">
         <is>
           <t>Georgia</t>
         </is>
       </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C6" t="b">
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D6" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
+      <c r="A7" t="n">
+        <v>6</v>
+      </c>
+      <c r="B7" t="inlineStr">
         <is>
           <t>Georgia</t>
         </is>
       </c>
-      <c r="B7" t="inlineStr">
+      <c r="C7" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C7" t="b">
+      <c r="D7" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr">
+      <c r="A8" t="n">
+        <v>7</v>
+      </c>
+      <c r="B8" t="inlineStr">
         <is>
           <t>Illinois</t>
         </is>
       </c>
-      <c r="B8" t="inlineStr">
+      <c r="C8" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C8" t="b">
+      <c r="D8" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="9">
-      <c r="A9" t="inlineStr">
+      <c r="A9" t="n">
+        <v>8</v>
+      </c>
+      <c r="B9" t="inlineStr">
         <is>
           <t>Iowa</t>
         </is>
       </c>
-      <c r="B9" t="inlineStr">
+      <c r="C9" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C9" t="b">
+      <c r="D9" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="10">
-      <c r="A10" t="inlineStr">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="inlineStr">
         <is>
           <t>Maine</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr">
+      <c r="C10" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C10" t="b">
+      <c r="D10" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="11">
-      <c r="A11" t="inlineStr">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="inlineStr">
         <is>
           <t>Maryland</t>
         </is>
       </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C11" t="b">
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" t="inlineStr">
+      <c r="A12" t="n">
+        <v>11</v>
+      </c>
+      <c r="B12" t="inlineStr">
         <is>
           <t>Massachusetts</t>
         </is>
       </c>
-      <c r="B12" t="inlineStr">
+      <c r="C12" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C12" t="b">
+      <c r="D12" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
+      <c r="A13" t="n">
+        <v>12</v>
+      </c>
+      <c r="B13" t="inlineStr">
         <is>
           <t>Michigan</t>
         </is>
       </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C13" t="b">
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D13" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="A14" t="n">
+        <v>13</v>
+      </c>
+      <c r="B14" t="inlineStr">
         <is>
           <t>Michigan</t>
         </is>
       </c>
-      <c r="B14" t="inlineStr">
+      <c r="C14" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C14" t="b">
+      <c r="D14" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
+      <c r="A15" t="n">
+        <v>14</v>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>Minnesota</t>
         </is>
       </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C15" t="b">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D15" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
+      <c r="A16" t="n">
+        <v>15</v>
+      </c>
+      <c r="B16" t="inlineStr">
         <is>
           <t>Minnesota</t>
         </is>
       </c>
-      <c r="B16" t="inlineStr">
+      <c r="C16" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C16" t="b">
+      <c r="D16" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr">
+      <c r="A17" t="n">
+        <v>16</v>
+      </c>
+      <c r="B17" t="inlineStr">
         <is>
           <t>New Hampshire</t>
         </is>
       </c>
-      <c r="B17" t="inlineStr">
+      <c r="C17" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C17" t="b">
+      <c r="D17" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
+      <c r="A18" t="n">
+        <v>17</v>
+      </c>
+      <c r="B18" t="inlineStr">
         <is>
           <t>New Mexico</t>
         </is>
       </c>
-      <c r="B18" t="inlineStr">
+      <c r="C18" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C18" t="b">
+      <c r="D18" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
+      <c r="A19" t="n">
+        <v>18</v>
+      </c>
+      <c r="B19" t="inlineStr">
         <is>
           <t>New York</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C19" t="b">
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D19" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
+      <c r="A20" t="n">
+        <v>19</v>
+      </c>
+      <c r="B20" t="inlineStr">
         <is>
           <t>North Carolina</t>
         </is>
       </c>
-      <c r="B20" t="inlineStr">
+      <c r="C20" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C20" t="b">
+      <c r="D20" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
+      <c r="A21" t="n">
+        <v>20</v>
+      </c>
+      <c r="B21" t="inlineStr">
         <is>
           <t>Ohio</t>
         </is>
       </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C21" t="b">
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D21" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="22">
-      <c r="A22" t="inlineStr">
+      <c r="A22" t="n">
+        <v>21</v>
+      </c>
+      <c r="B22" t="inlineStr">
         <is>
           <t>Oregon</t>
         </is>
       </c>
-      <c r="B22" t="inlineStr">
+      <c r="C22" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C22" t="b">
+      <c r="D22" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="23">
-      <c r="A23" t="inlineStr">
+      <c r="A23" t="n">
+        <v>22</v>
+      </c>
+      <c r="B23" t="inlineStr">
         <is>
           <t>Pennsylvania</t>
         </is>
       </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C23" t="b">
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D23" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="24">
-      <c r="A24" t="inlineStr">
+      <c r="A24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B24" t="inlineStr">
         <is>
           <t>Texas</t>
         </is>
       </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C24" t="b">
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D24" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
+      <c r="A25" t="n">
+        <v>24</v>
+      </c>
+      <c r="B25" t="inlineStr">
         <is>
           <t>Texas</t>
         </is>
       </c>
-      <c r="B25" t="inlineStr">
+      <c r="C25" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C25" t="b">
+      <c r="D25" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr">
+      <c r="A26" t="n">
+        <v>25</v>
+      </c>
+      <c r="B26" t="inlineStr">
         <is>
           <t>Virginia</t>
         </is>
       </c>
-      <c r="B26" t="inlineStr">
+      <c r="C26" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C26" t="b">
+      <c r="D26" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="27">
-      <c r="A27" t="inlineStr">
+      <c r="A27" t="n">
+        <v>26</v>
+      </c>
+      <c r="B27" t="inlineStr">
         <is>
           <t>Wisconsin</t>
         </is>
       </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C27" t="b">
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D27" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="28">
-      <c r="A28" t="inlineStr">
+      <c r="A28" t="n">
+        <v>27</v>
+      </c>
+      <c r="B28" t="inlineStr">
         <is>
           <t>Colorado</t>
         </is>
       </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C28" t="b">
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D28" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="29">
-      <c r="A29" t="inlineStr">
+      <c r="A29" t="n">
+        <v>28</v>
+      </c>
+      <c r="B29" t="inlineStr">
         <is>
           <t>Nevada</t>
         </is>
       </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C29" t="b">
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D29" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="30">
-      <c r="A30" t="inlineStr">
+      <c r="A30" t="n">
+        <v>29</v>
+      </c>
+      <c r="B30" t="inlineStr">
         <is>
           <t>Illinois</t>
         </is>
       </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C30" t="b">
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D30" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>30</v>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Oregon</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D31" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>31</v>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>Connecticut</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D32" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>New Hampshire</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D33" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>Kansas</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D34" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>New Mexico</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D35" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>Iowa</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D36" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>Maine</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>Kentucky</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D38" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>39</v>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>New Jersey</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D39" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>40</v>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>Florida</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D40" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>41</v>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>Ohio</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D41" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Oregon</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C31" t="b">
+    <row r="42">
+      <c r="A42" t="n">
+        <v>42</v>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D42" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>Connecticut</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C32" t="b">
+    <row r="43">
+      <c r="A43" t="n">
+        <v>43</v>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>Massachusetts</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D43" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>New Hampshire</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C33" t="b">
+    <row r="44">
+      <c r="A44" t="n">
+        <v>44</v>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>Delaware</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D44" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
+    <row r="45">
+      <c r="A45" t="n">
+        <v>45</v>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D45" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>46</v>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>West Virginia</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D46" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>47</v>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D47" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>48</v>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Kansas</t>
         </is>
       </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C34" t="b">
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D48" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>New Mexico</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C35" t="b">
+    <row r="49">
+      <c r="A49" t="n">
+        <v>49</v>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D49" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>Iowa</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C36" t="b">
+    <row r="50">
+      <c r="A50" t="n">
+        <v>50</v>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D50" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>Maine</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C37" t="b">
+    <row r="51">
+      <c r="A51" t="n">
+        <v>51</v>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D51" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>Kentucky</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="n">
+        <v>52</v>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>Alabama</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
         <is>
           <t>Senate</t>
         </is>
       </c>
-      <c r="C38" t="b">
+      <c r="D52" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
+    <row r="53">
+      <c r="A53" t="n">
+        <v>53</v>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D53" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>54</v>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D54" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>55</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>Louisiana</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D55" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>56</v>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>Mississippi</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D56" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>57</v>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>Montana</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D57" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>58</v>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D58" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>59</v>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>Senate</t>
+        </is>
+      </c>
+      <c r="D59" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>60</v>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>Alaska</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D60" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>61</v>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>Arkansas</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D61" t="b">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>62</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>Hawaii</t>
         </is>
       </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C39" t="b">
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D62" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>New Jersey</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C40" t="b">
+    <row r="63">
+      <c r="A63" t="n">
+        <v>63</v>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Idaho</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D63" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="41">
-      <c r="A41" t="inlineStr">
-        <is>
-          <t>Florida</t>
-        </is>
-      </c>
-      <c r="B41" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C41" t="b">
+    <row r="64">
+      <c r="A64" t="n">
+        <v>64</v>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Nebraska</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D64" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="42">
-      <c r="A42" t="inlineStr">
-        <is>
-          <t>Ohio</t>
-        </is>
-      </c>
-      <c r="B42" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C42" t="b">
+    <row r="65">
+      <c r="A65" t="n">
+        <v>65</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>Oklahoma</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D65" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="43">
-      <c r="A43" t="inlineStr">
-        <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="B43" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C43" t="b">
+    <row r="66">
+      <c r="A66" t="n">
+        <v>66</v>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Rhode Island</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D66" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
-        <is>
-          <t>Massachusetts</t>
-        </is>
-      </c>
-      <c r="B44" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C44" t="b">
+    <row r="67">
+      <c r="A67" t="n">
+        <v>67</v>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>South Carolina</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D67" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
-        <is>
-          <t>Delaware</t>
-        </is>
-      </c>
-      <c r="B45" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C45" t="b">
+    <row r="68">
+      <c r="A68" t="n">
+        <v>68</v>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>South Dakota</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D68" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C46" t="b">
+    <row r="69">
+      <c r="A69" t="n">
+        <v>69</v>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>Tennessee</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D69" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>West Virginia</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C47" t="b">
+    <row r="70">
+      <c r="A70" t="n">
+        <v>70</v>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Vermont</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D70" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C48" t="b">
+    <row r="71">
+      <c r="A71" t="n">
+        <v>71</v>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Wyoming</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D71" t="b">
         <v>0</v>
       </c>
     </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>Kansas</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C49" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C50" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C51" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C52" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
+    <row r="72">
+      <c r="A72" t="n">
+        <v>72</v>
+      </c>
+      <c r="B72" t="inlineStr">
         <is>
           <t>Alabama</t>
         </is>
       </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C53" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" t="inlineStr">
-        <is>
-          <t>Arkansas</t>
-        </is>
-      </c>
-      <c r="B54" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C54" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" t="inlineStr">
-        <is>
-          <t>Idaho</t>
-        </is>
-      </c>
-      <c r="B55" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C55" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" t="inlineStr">
-        <is>
-          <t>Louisiana</t>
-        </is>
-      </c>
-      <c r="B56" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C56" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" t="inlineStr">
-        <is>
-          <t>Mississippi</t>
-        </is>
-      </c>
-      <c r="B57" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C57" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" t="inlineStr">
-        <is>
-          <t>Montana</t>
-        </is>
-      </c>
-      <c r="B58" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C58" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
-        </is>
-      </c>
-      <c r="B59" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C59" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
-      <c r="B60" t="inlineStr">
-        <is>
-          <t>Senate</t>
-        </is>
-      </c>
-      <c r="C60" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" t="inlineStr">
-        <is>
-          <t>Alaska</t>
-        </is>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C61" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" t="inlineStr">
-        <is>
-          <t>Arkansas</t>
-        </is>
-      </c>
-      <c r="B62" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C62" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" t="inlineStr">
-        <is>
-          <t>Hawaii</t>
-        </is>
-      </c>
-      <c r="B63" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C63" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" t="inlineStr">
-        <is>
-          <t>Idaho</t>
-        </is>
-      </c>
-      <c r="B64" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C64" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>Nebraska</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C65" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>Oklahoma</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C66" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>Rhode Island</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C67" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>South Carolina</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C68" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>South Dakota</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C69" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>Tennessee</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C70" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" t="inlineStr">
-        <is>
-          <t>Vermont</t>
-        </is>
-      </c>
-      <c r="B71" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C71" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" t="inlineStr">
-        <is>
-          <t>Wyoming</t>
-        </is>
-      </c>
-      <c r="B72" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C72" t="b">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="73">
-      <c r="A73" t="inlineStr">
-        <is>
-          <t>Alabama</t>
-        </is>
-      </c>
-      <c r="B73" t="inlineStr">
-        <is>
-          <t>Governor</t>
-        </is>
-      </c>
-      <c r="C73" t="b">
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Governor</t>
+        </is>
+      </c>
+      <c r="D72" t="b">
         <v>0</v>
       </c>
     </row>
